--- a/fixtures/Planned_blade_work_2026.xlsx
+++ b/fixtures/Planned_blade_work_2026.xlsx
@@ -457,7 +457,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>GBCMA.ROB01WF.GH04.MDA11</v>
+        <v>ACME.OWF01.GT04.MDA11</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -490,13 +490,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M2" t="str">
         <v>MECH</v>
       </c>
       <c r="N2" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O2" t="str">
         <v>GB</v>
@@ -513,7 +513,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GBCMA.ROB01WF.GF04.MDA12</v>
+        <v>ACME.OWF01.GT09.MDA12</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -546,13 +546,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M3" t="str">
         <v>MECH</v>
       </c>
       <c r="N3" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O3" t="str">
         <v>GB</v>
@@ -569,7 +569,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GBCMA.ROB01WF.GC04.MDA13</v>
+        <v>ACME.OWF01.GT14.MDA13</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -602,13 +602,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M4" t="str">
         <v>MECH</v>
       </c>
       <c r="N4" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O4" t="str">
         <v>GB</v>
@@ -625,7 +625,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GBCMA.ROB01WF.GD06.MDA13</v>
+        <v>ACME.OWF01.GT19.MDA13</v>
       </c>
       <c r="B5" t="str">
         <v/>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="L5" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M5" t="str">
         <v>MECH</v>
       </c>
       <c r="N5" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O5" t="str">
         <v>GB</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>GBCMA.ROB01WF.GG03.MDA13</v>
+        <v>ACME.OWF01.GT23.MDA13</v>
       </c>
       <c r="B6" t="str">
         <v/>
@@ -714,13 +714,13 @@
         <v>0</v>
       </c>
       <c r="L6" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M6" t="str">
         <v>MECH</v>
       </c>
       <c r="N6" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O6" t="str">
         <v>GB</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>GBCMA.ROB01WF.GA02.MDA11</v>
+        <v>ACME.OWF01.GT27.MDA11</v>
       </c>
       <c r="B7" t="str">
         <v/>
@@ -770,13 +770,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M7" t="str">
         <v>MECH</v>
       </c>
       <c r="N7" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O7" t="str">
         <v>GB</v>
@@ -793,7 +793,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>GBCMA.ROB01WF.GF02.MDA13</v>
+        <v>ACME.OWF01.GT31.MDA13</v>
       </c>
       <c r="B8" t="str">
         <v/>
@@ -826,13 +826,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M8" t="str">
         <v>MECH</v>
       </c>
       <c r="N8" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O8" t="str">
         <v>GB</v>
@@ -849,7 +849,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>GBCMA.ROB01WF.GD02.MDA11</v>
+        <v>ACME.OWF01.GT35.MDA11</v>
       </c>
       <c r="B9" t="str">
         <v/>
@@ -882,13 +882,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M9" t="str">
         <v>MECH</v>
       </c>
       <c r="N9" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O9" t="str">
         <v>GB</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>GBCMA.ROB01WF.GD02.MDA13</v>
+        <v>ACME.OWF01.GT35.MDA13</v>
       </c>
       <c r="B10" t="str">
         <v/>
@@ -938,13 +938,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M10" t="str">
         <v>MECH</v>
       </c>
       <c r="N10" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O10" t="str">
         <v>GB</v>
@@ -961,7 +961,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>GBCMA.ROB01WF.GD04.MDA12</v>
+        <v>ACME.OWF01.GT39.MDA12</v>
       </c>
       <c r="B11" t="str">
         <v/>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M11" t="str">
         <v>MECH</v>
       </c>
       <c r="N11" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O11" t="str">
         <v>GB</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>GBCMA.ROB01WF.GD03.MDA13</v>
+        <v>ACME.OWF01.GT43.MDA13</v>
       </c>
       <c r="B12" t="str">
         <v/>
@@ -1050,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M12" t="str">
         <v>MECH</v>
       </c>
       <c r="N12" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O12" t="str">
         <v>GB</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>GBCMA.ROB01WF.GG07.MDA11</v>
+        <v>ACME.OWF01.GT47.MDA11</v>
       </c>
       <c r="B13" t="str">
         <v/>
@@ -1106,13 +1106,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M13" t="str">
         <v>MECH</v>
       </c>
       <c r="N13" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O13" t="str">
         <v>GB</v>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>GBCMA.ROB01WF.GD07.MDA13</v>
+        <v>ACME.OWF01.GT51.MDA13</v>
       </c>
       <c r="B14" t="str">
         <v/>
@@ -1162,13 +1162,13 @@
         <v>0</v>
       </c>
       <c r="L14" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M14" t="str">
         <v>MECH</v>
       </c>
       <c r="N14" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O14" t="str">
         <v>GB</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>GBCMA.ROB01WF.GE02.MDA11</v>
+        <v>ACME.OWF01.GT55.MDA11</v>
       </c>
       <c r="B15" t="str">
         <v/>
@@ -1218,13 +1218,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M15" t="str">
         <v>MECH</v>
       </c>
       <c r="N15" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O15" t="str">
         <v>GB</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>GBCMA.ROB01WF.GE02.MDA12</v>
+        <v>ACME.OWF01.GT55.MDA12</v>
       </c>
       <c r="B16" t="str">
         <v/>
@@ -1274,13 +1274,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M16" t="str">
         <v>MECH</v>
       </c>
       <c r="N16" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O16" t="str">
         <v>GB</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>GBCMA.ROB01WF.GH03.MDA12</v>
+        <v>ACME.OWF01.GT59.MDA12</v>
       </c>
       <c r="B17" t="str">
         <v/>
@@ -1330,13 +1330,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M17" t="str">
         <v>MECH</v>
       </c>
       <c r="N17" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O17" t="str">
         <v>GB</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>GBCMA.ROB01WF.GH05.MDA11</v>
+        <v>ACME.OWF01.GT63.MDA11</v>
       </c>
       <c r="B18" t="str">
         <v/>
@@ -1386,13 +1386,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M18" t="str">
         <v>MECH</v>
       </c>
       <c r="N18" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O18" t="str">
         <v>GB</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>GBCMA.ROB01WF.GF05.MDA13</v>
+        <v>ACME.OWF01.GT67.MDA13</v>
       </c>
       <c r="B19" t="str">
         <v/>
@@ -1442,13 +1442,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="M19" t="str">
         <v>MECH</v>
       </c>
       <c r="N19" t="str">
-        <v>ROB1</v>
+        <v>ACM1</v>
       </c>
       <c r="O19" t="str">
         <v>GB</v>
